--- a/manuscript/ESM_2.xlsx
+++ b/manuscript/ESM_2.xlsx
@@ -10856,10 +10856,10 @@
         <v>79</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>0.8481012658227848</v>
       </c>
     </row>
     <row r="8">
@@ -11260,10 +11260,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>16.66666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
